--- a/data/raw/returns/viomi.xlsx
+++ b/data/raw/returns/viomi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L667"/>
+  <dimension ref="A1:L666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37926,62 +37926,6 @@
       </c>
       <c r="L666" t="inlineStr"/>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>2026-04-21T15:16:37+00:00</t>
-        </is>
-      </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>402-3309650-2122735</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr">
-        <is>
-          <t>FBA79812</t>
-        </is>
-      </c>
-      <c r="D667" t="inlineStr">
-        <is>
-          <t>B0FS6TB7CP</t>
-        </is>
-      </c>
-      <c r="E667" t="inlineStr">
-        <is>
-          <t>X002F3JZP9</t>
-        </is>
-      </c>
-      <c r="F667" t="inlineStr">
-        <is>
-          <t>NexLev Portable Blender for Smoothies Milkshakes Juices Baby Food | High Borosilicate Glass Jar | 3000 mAh Battery | Type C | Mix Fruit Juicer Mini | 450ml | For Kitchen &amp; Travel | PB-01</t>
-        </is>
-      </c>
-      <c r="G667" t="n">
-        <v>1</v>
-      </c>
-      <c r="H667" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I667" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J667" t="inlineStr">
-        <is>
-          <t>UNDELIVERABLE_REFUSED</t>
-        </is>
-      </c>
-      <c r="K667" t="inlineStr">
-        <is>
-          <t>LPNBLR5P1916899</t>
-        </is>
-      </c>
-      <c r="L667" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/raw/returns/viomi.xlsx
+++ b/data/raw/returns/viomi.xlsx
@@ -6661,7 +6661,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970149</t>
+          <t>LPNBLR5P8970159</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970159</t>
+          <t>LPNBLR5P8970149</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>

--- a/data/raw/returns/viomi.xlsx
+++ b/data/raw/returns/viomi.xlsx
@@ -6773,7 +6773,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970149</t>
+          <t>LPNBLR5P8970159</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970159</t>
+          <t>LPNBLR5P8970149</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>

--- a/data/raw/returns/viomi.xlsx
+++ b/data/raw/returns/viomi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L708"/>
+  <dimension ref="A1:L707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970159</t>
+          <t>LPNBLR5P8970149</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970149</t>
+          <t>LPNBLR5P8970159</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
@@ -40225,62 +40225,6 @@
         </is>
       </c>
       <c r="L707" t="inlineStr"/>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>2026-05-05T12:38:52+00:00</t>
-        </is>
-      </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>404-3145597-2518723</t>
-        </is>
-      </c>
-      <c r="C708" t="inlineStr">
-        <is>
-          <t>FBA79493</t>
-        </is>
-      </c>
-      <c r="D708" t="inlineStr">
-        <is>
-          <t>B0DQCWRG3H</t>
-        </is>
-      </c>
-      <c r="E708" t="inlineStr">
-        <is>
-          <t>X0028X1G99</t>
-        </is>
-      </c>
-      <c r="F708" t="inlineStr">
-        <is>
-          <t>NexLev Ionic 3 in 1 Hot Air Brush|1.5 Inch Barrel |Volumizer Blow Dryer &amp; Styler|Ceramic Tourmaline Coated for Heat Protection|1200W|Dual Bristle for Tangle Free Styling|Salon Like Styles at Home|V-03</t>
-        </is>
-      </c>
-      <c r="G708" t="n">
-        <v>1</v>
-      </c>
-      <c r="H708" t="inlineStr">
-        <is>
-          <t>DEL2</t>
-        </is>
-      </c>
-      <c r="I708" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J708" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
-      <c r="K708" t="inlineStr">
-        <is>
-          <t>LPNDEL2R76588075</t>
-        </is>
-      </c>
-      <c r="L708" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/viomi.xlsx
+++ b/data/raw/returns/viomi.xlsx
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970149</t>
+          <t>LPNBLR5P8970159</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970159</t>
+          <t>LPNBLR5P8970149</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>

--- a/data/raw/returns/viomi.xlsx
+++ b/data/raw/returns/viomi.xlsx
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970159</t>
+          <t>LPNBLR5P8970149</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970149</t>
+          <t>LPNBLR5P8970159</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>

--- a/data/raw/returns/viomi.xlsx
+++ b/data/raw/returns/viomi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L717"/>
+  <dimension ref="A1:L716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40730,62 +40730,6 @@
       </c>
       <c r="L716" t="inlineStr"/>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>2026-05-13T05:50:53+00:00</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>403-4655694-5079566</t>
-        </is>
-      </c>
-      <c r="C717" t="inlineStr">
-        <is>
-          <t>FBK79788</t>
-        </is>
-      </c>
-      <c r="D717" t="inlineStr">
-        <is>
-          <t>B0FN4D3C89</t>
-        </is>
-      </c>
-      <c r="E717" t="inlineStr">
-        <is>
-          <t>X002DVGH59</t>
-        </is>
-      </c>
-      <c r="F717" t="inlineStr">
-        <is>
-          <t>White Mulberry Economy Fixed TV Wall Mount Bracket for 13-43 Inches |45kg|LED/LCD/Smart TV's, Universal VESA Compatible 75x75,200x200 mm MAX Slim Wall Mount Stand</t>
-        </is>
-      </c>
-      <c r="G717" t="n">
-        <v>1</v>
-      </c>
-      <c r="H717" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I717" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J717" t="inlineStr">
-        <is>
-          <t>NO_REASON_GIVEN</t>
-        </is>
-      </c>
-      <c r="K717" t="inlineStr">
-        <is>
-          <t>LPNBLR5P4003578</t>
-        </is>
-      </c>
-      <c r="L717" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/raw/returns/viomi.xlsx
+++ b/data/raw/returns/viomi.xlsx
@@ -17509,7 +17509,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970159</t>
+          <t>LPNBLR5P8970149</t>
         </is>
       </c>
       <c r="L304" t="inlineStr"/>
@@ -17565,7 +17565,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>LPNBLR5P8970149</t>
+          <t>LPNBLR5P8970159</t>
         </is>
       </c>
       <c r="L305" t="inlineStr"/>

--- a/data/raw/returns/viomi.xlsx
+++ b/data/raw/returns/viomi.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L684"/>
+  <dimension ref="A1:L683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38886,62 +38886,6 @@
       </c>
       <c r="L683" t="inlineStr"/>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>2026-06-03T10:27:45+00:00</t>
-        </is>
-      </c>
-      <c r="B684" t="inlineStr">
-        <is>
-          <t>405-3011821-8988320</t>
-        </is>
-      </c>
-      <c r="C684" t="inlineStr">
-        <is>
-          <t>FBK79789</t>
-        </is>
-      </c>
-      <c r="D684" t="inlineStr">
-        <is>
-          <t>B0FN4DSQ6P</t>
-        </is>
-      </c>
-      <c r="E684" t="inlineStr">
-        <is>
-          <t>X002DV4SQJ</t>
-        </is>
-      </c>
-      <c r="F684" t="inlineStr">
-        <is>
-          <t>White Mulberry Premium Economy Fixed TV Wall Mount Bracket for 32-65 Inches |45kg| LED/LCD/OLED/Smart &amp; Curved TV's, VESA 50x50, 400x400 MAX, Slim Wall Stand</t>
-        </is>
-      </c>
-      <c r="G684" t="n">
-        <v>1</v>
-      </c>
-      <c r="H684" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I684" t="inlineStr">
-        <is>
-          <t>CARRIER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J684" t="inlineStr">
-        <is>
-          <t>NOT_COMPATIBLE</t>
-        </is>
-      </c>
-      <c r="K684" t="inlineStr">
-        <is>
-          <t>LPNBLR5P7778615</t>
-        </is>
-      </c>
-      <c r="L684" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
